--- a/SuppXLS/trades/ScenTrade_TRADE_PARMS.xlsx
+++ b/SuppXLS/trades/ScenTrade_TRADE_PARMS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\weerasa\TIMES-NZ-Model-Files\TIMES-NZ\SuppXLS\Trades\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F69BB470-D42C-4F64-8352-3FECE5AE48AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC3D8B1-E867-4230-A095-4447DB408927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documentation" sheetId="3" r:id="rId1"/>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="73">
   <si>
     <t>Pset_CI</t>
   </si>
@@ -397,14 +397,17 @@
   <si>
     <t>INS: Attribute specifications for the trade processes</t>
   </si>
+  <si>
+    <t>TU_ELCNGA</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="10">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _D_M_-;\-* #,##0.00\ _D_M_-;_-* &quot;-&quot;??\ _D_M_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-[$€-2]* #,##0.00_-;\-[$€-2]* #,##0.00_-;_-[$€-2]* &quot;-&quot;??_-"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
@@ -1678,15 +1681,63 @@
     <xf numFmtId="0" fontId="57" fillId="47" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="57" fillId="47" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="57" fillId="47" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="47" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1698,6 +1749,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1706,67 +1758,18 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="7">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
@@ -1934,15 +1937,15 @@
     <xf numFmtId="0" fontId="63" fillId="49" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="63" fillId="49" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
@@ -7517,11 +7520,11 @@
     <xf numFmtId="0" fontId="10" fillId="26" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="4" fontId="29" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="76" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="76" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="76" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -7540,7 +7543,7 @@
     <xf numFmtId="11" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="2475" applyFont="1"/>
     <xf numFmtId="2" fontId="76" fillId="0" borderId="0" xfId="2475" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="53" fillId="0" borderId="0" xfId="2476" applyFont="1"/>
+    <xf numFmtId="164" fontId="53" fillId="0" borderId="0" xfId="2476" applyFont="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="2475" applyFont="1"/>
     <xf numFmtId="0" fontId="75" fillId="52" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="75" fillId="52" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -7548,6 +7551,7 @@
     <xf numFmtId="0" fontId="73" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="74" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="172" fontId="75" fillId="52" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="75" fillId="52" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2479">
     <cellStyle name="20 % - Accent1" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -10399,14 +10403,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88AB4833-8249-4DD2-AACE-7839DE5841F5}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>71</v>
       </c>
@@ -10419,30 +10423,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R145"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="13.15" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="11"/>
-    <col min="2" max="2" width="18.1796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.54296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" style="11" customWidth="1"/>
-    <col min="5" max="5" width="9.26953125" style="11" customWidth="1"/>
-    <col min="6" max="6" width="11.54296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7265625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="9.19921875" style="11"/>
+    <col min="2" max="2" width="18.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.53125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.46484375" style="11" customWidth="1"/>
+    <col min="5" max="5" width="9.265625" style="11" customWidth="1"/>
+    <col min="6" max="6" width="11.53125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.73046875" style="11" customWidth="1"/>
     <col min="8" max="8" width="20" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.54296875" style="11" customWidth="1"/>
-    <col min="10" max="10" width="8.453125" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.54296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="8.453125" style="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.1796875" style="11"/>
+    <col min="9" max="9" width="21.53125" style="11" customWidth="1"/>
+    <col min="10" max="10" width="8.46484375" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.53125" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.73046875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.46484375" style="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.19921875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
@@ -10453,7 +10457,7 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
@@ -10497,7 +10501,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7" t="s">
@@ -10522,7 +10526,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7" t="s">
@@ -10544,7 +10548,7 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7" t="s">
@@ -10572,7 +10576,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7" t="s">
@@ -10594,7 +10598,7 @@
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7" t="s">
@@ -10619,7 +10623,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7" t="s">
@@ -10647,7 +10651,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7" t="s">
@@ -10675,7 +10679,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7" t="s">
@@ -10699,7 +10703,7 @@
       <c r="N11" s="7"/>
       <c r="O11" s="18"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7" t="s">
@@ -10722,7 +10726,7 @@
       <c r="N12" s="7"/>
       <c r="O12" s="18"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
       <c r="D13" s="7" t="s">
@@ -10745,15 +10749,22 @@
       <c r="N13" s="7"/>
       <c r="O13" s="18"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
+      <c r="D14" s="18" t="s">
+        <v>18</v>
+      </c>
       <c r="E14" s="18"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="19"/>
+      <c r="G14" s="24">
+        <f>1/3.6</f>
+        <v>0.27777777777777779</v>
+      </c>
       <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
+      <c r="I14" s="18" t="s">
+        <v>72</v>
+      </c>
       <c r="J14" s="18"/>
       <c r="K14" s="18"/>
       <c r="L14" s="18"/>
@@ -10761,7 +10772,7 @@
       <c r="N14" s="18"/>
       <c r="O14" s="18"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -10777,7 +10788,7 @@
       <c r="N15" s="18"/>
       <c r="O15" s="18"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -10793,7 +10804,7 @@
       <c r="N16" s="18"/>
       <c r="O16" s="18"/>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B18" s="1"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -10802,7 +10813,7 @@
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B19" s="3" t="s">
         <v>9</v>
       </c>
@@ -10843,7 +10854,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
@@ -10858,7 +10869,7 @@
       <c r="M20" s="7"/>
       <c r="N20" s="7"/>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B23" s="1"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
@@ -10867,7 +10878,7 @@
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B24" s="3" t="s">
         <v>9</v>
       </c>
@@ -10908,7 +10919,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
@@ -10923,7 +10934,7 @@
       <c r="M26" s="7"/>
       <c r="N26" s="7"/>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B28" s="1"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
@@ -10932,7 +10943,7 @@
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B29" s="3" t="s">
         <v>9</v>
       </c>
@@ -10973,7 +10984,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
       <c r="D30" s="20"/>
@@ -10988,7 +10999,7 @@
       <c r="M30" s="22"/>
       <c r="N30" s="22"/>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7" t="s">
@@ -11004,7 +11015,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
@@ -11019,7 +11030,7 @@
       <c r="M32" s="7"/>
       <c r="N32" s="7"/>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B35" s="1" t="s">
         <v>8</v>
       </c>
@@ -11030,7 +11041,7 @@
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B36" s="3" t="s">
         <v>9</v>
       </c>
@@ -11074,7 +11085,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7" t="s">
@@ -11100,7 +11111,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7" t="s">
@@ -11123,7 +11134,7 @@
       <c r="N38" s="7"/>
       <c r="O38" s="7"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.4">
       <c r="D39" s="7" t="s">
         <v>30</v>
       </c>
@@ -11135,7 +11146,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.4">
       <c r="D40" s="7" t="s">
         <v>30</v>
       </c>
@@ -11147,7 +11158,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.4">
       <c r="D41" s="7" t="s">
         <v>30</v>
       </c>
@@ -11159,7 +11170,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.4">
       <c r="D42" s="7" t="s">
         <v>30</v>
       </c>
@@ -11171,7 +11182,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.4">
       <c r="D43" s="7" t="s">
         <v>30</v>
       </c>
@@ -11183,7 +11194,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.4">
       <c r="D44" s="7" t="s">
         <v>30</v>
       </c>
@@ -11195,7 +11206,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.4">
       <c r="D45" s="7" t="s">
         <v>30</v>
       </c>
@@ -11207,7 +11218,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.4">
       <c r="D46" s="7" t="s">
         <v>30</v>
       </c>
@@ -11219,12 +11230,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.4">
       <c r="D47" s="7"/>
       <c r="G47" s="12"/>
       <c r="I47" s="7"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.4">
       <c r="D48" s="7" t="s">
         <v>30</v>
       </c>
@@ -11236,10 +11247,10 @@
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A49" s="13"/>
     </row>
-    <row r="51" spans="1:14" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14" ht="14.25" x14ac:dyDescent="0.45">
       <c r="G51" s="11">
         <v>1703</v>
       </c>
@@ -11259,7 +11270,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:14" ht="14.25" x14ac:dyDescent="0.45">
       <c r="F52" s="11" t="s">
         <v>40</v>
       </c>
@@ -11276,7 +11287,7 @@
         <v>44.039985656738281</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14" ht="14.25" x14ac:dyDescent="0.45">
       <c r="F53" s="11" t="s">
         <v>41</v>
       </c>
@@ -11293,7 +11304,7 @@
         <v>43.859966278076172</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:14" ht="14.25" x14ac:dyDescent="0.45">
       <c r="K54" s="14" t="s">
         <v>45</v>
       </c>
@@ -11301,7 +11312,7 @@
         <v>43.887393770091592</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:14" ht="14.25" x14ac:dyDescent="0.45">
       <c r="K55" s="14" t="s">
         <v>46</v>
       </c>
@@ -11309,7 +11320,7 @@
         <v>43.109966278076172</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:14" ht="14.25" x14ac:dyDescent="0.45">
       <c r="K56" s="14" t="s">
         <v>47</v>
       </c>
@@ -11317,7 +11328,7 @@
         <v>41.619983673095703</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:14" ht="14.25" x14ac:dyDescent="0.45">
       <c r="K57" s="14" t="s">
         <v>48</v>
       </c>
@@ -11325,7 +11336,7 @@
         <v>40.647428543255998</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:14" ht="14.25" x14ac:dyDescent="0.45">
       <c r="K58" s="14" t="s">
         <v>49</v>
       </c>
@@ -11333,7 +11344,7 @@
         <v>40.32934942720064</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:14" ht="14.25" x14ac:dyDescent="0.45">
       <c r="K59" s="14" t="s">
         <v>50</v>
       </c>
@@ -11341,7 +11352,7 @@
         <v>43.42095279018293</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:14" ht="14.25" x14ac:dyDescent="0.45">
       <c r="K60" s="14" t="s">
         <v>51</v>
       </c>
@@ -11349,7 +11360,7 @@
         <v>44.5</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:14" ht="14.25" x14ac:dyDescent="0.45">
       <c r="K61" s="14" t="s">
         <v>52</v>
       </c>
@@ -11357,13 +11368,13 @@
         <v>43.6</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:14" ht="14.25" x14ac:dyDescent="0.45">
       <c r="K63" s="17" t="s">
         <v>54</v>
       </c>
       <c r="L63" s="16"/>
     </row>
-    <row r="64" spans="1:14" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:14" ht="14.25" x14ac:dyDescent="0.45">
       <c r="K64" s="14" t="s">
         <v>27</v>
       </c>
@@ -11371,7 +11382,7 @@
         <v>20.247535759282592</v>
       </c>
     </row>
-    <row r="66" spans="11:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K66" s="11" t="s">
         <v>28</v>
       </c>
@@ -11379,7 +11390,7 @@
         <v>26.59</v>
       </c>
     </row>
-    <row r="67" spans="11:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K67" s="11" t="s">
         <v>29</v>
       </c>
@@ -11387,15 +11398,15 @@
         <v>15.27</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A98" s="13"/>
     </row>
-    <row r="115" spans="15:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="15:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="O115" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A145" s="13"/>
     </row>
   </sheetData>

--- a/SuppXLS/trades/ScenTrade_TRADE_PARMS.xlsx
+++ b/SuppXLS/trades/ScenTrade_TRADE_PARMS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC3D8B1-E867-4230-A095-4447DB408927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07FA12D-7597-41ED-93A0-401FE0AF605E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -398,7 +398,7 @@
     <t>INS: Attribute specifications for the trade processes</t>
   </si>
   <si>
-    <t>TU_ELCNGA</t>
+    <t>TU_ELC???</t>
   </si>
 </sst>
 </file>
